--- a/ejemplos-generados/gestion-departamento.xlsx
+++ b/ejemplos-generados/gestion-departamento.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07/09/2026 16:52</t>
+          <t>07/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
   <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>

--- a/ejemplos-generados/gestion-departamento.xlsx
+++ b/ejemplos-generados/gestion-departamento.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07/09/2026 16:55</t>
+          <t>07/09/2026 17:08</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
     </row>
     <row r="2"/>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Id</t>
@@ -5444,23 +5444,23 @@
         <v/>
       </c>
       <c r="G1">
-        <f>'Asignación'!B4</f>
+        <f>IF('Asignación'!B4="","",'Asignación'!B4)</f>
         <v/>
       </c>
       <c r="H1">
-        <f>'Asignación'!D4</f>
+        <f>IF('Asignación'!D4="","",'Asignación'!D4)</f>
         <v/>
       </c>
       <c r="I1">
-        <f>'Asignación'!E4</f>
+        <f>IF('Asignación'!E4="","",'Asignación'!E4)</f>
         <v/>
       </c>
       <c r="J1">
-        <f>'Asignación'!F4</f>
+        <f>IF('Asignación'!F4="","",'Asignación'!F4)</f>
         <v/>
       </c>
       <c r="L1">
-        <f>IF('Asignación'!$G$4="","",'Asignación'!$G$4&amp;"|"&amp;'Asignación'!$A$4)</f>
+        <f>IF(OR('Asignación'!$G$4="",'Asignación'!$A$4=""),"",'Asignación'!$G$4&amp;"|"&amp;'Asignación'!$A$4)</f>
         <v/>
       </c>
       <c r="M1">
@@ -5474,23 +5474,23 @@
         <v/>
       </c>
       <c r="G2">
-        <f>'Asignación'!B5</f>
+        <f>IF('Asignación'!B5="","",'Asignación'!B5)</f>
         <v/>
       </c>
       <c r="H2">
-        <f>'Asignación'!D5</f>
+        <f>IF('Asignación'!D5="","",'Asignación'!D5)</f>
         <v/>
       </c>
       <c r="I2">
-        <f>'Asignación'!E5</f>
+        <f>IF('Asignación'!E5="","",'Asignación'!E5)</f>
         <v/>
       </c>
       <c r="J2">
-        <f>'Asignación'!F5</f>
+        <f>IF('Asignación'!F5="","",'Asignación'!F5)</f>
         <v/>
       </c>
       <c r="L2">
-        <f>IF('Asignación'!$G$5="","",'Asignación'!$G$5&amp;"|"&amp;'Asignación'!$A$5)</f>
+        <f>IF(OR('Asignación'!$G$5="",'Asignación'!$A$5=""),"",'Asignación'!$G$5&amp;"|"&amp;'Asignación'!$A$5)</f>
         <v/>
       </c>
       <c r="M2">
@@ -5504,23 +5504,23 @@
         <v/>
       </c>
       <c r="G3">
-        <f>'Asignación'!B6</f>
+        <f>IF('Asignación'!B6="","",'Asignación'!B6)</f>
         <v/>
       </c>
       <c r="H3">
-        <f>'Asignación'!D6</f>
+        <f>IF('Asignación'!D6="","",'Asignación'!D6)</f>
         <v/>
       </c>
       <c r="I3">
-        <f>'Asignación'!E6</f>
+        <f>IF('Asignación'!E6="","",'Asignación'!E6)</f>
         <v/>
       </c>
       <c r="J3">
-        <f>'Asignación'!F6</f>
+        <f>IF('Asignación'!F6="","",'Asignación'!F6)</f>
         <v/>
       </c>
       <c r="L3">
-        <f>IF('Asignación'!$G$6="","",'Asignación'!$G$6&amp;"|"&amp;'Asignación'!$A$6)</f>
+        <f>IF(OR('Asignación'!$G$6="",'Asignación'!$A$6=""),"",'Asignación'!$G$6&amp;"|"&amp;'Asignación'!$A$6)</f>
         <v/>
       </c>
       <c r="M3">
@@ -5534,23 +5534,23 @@
         <v/>
       </c>
       <c r="G4">
-        <f>'Asignación'!B7</f>
+        <f>IF('Asignación'!B7="","",'Asignación'!B7)</f>
         <v/>
       </c>
       <c r="H4">
-        <f>'Asignación'!D7</f>
+        <f>IF('Asignación'!D7="","",'Asignación'!D7)</f>
         <v/>
       </c>
       <c r="I4">
-        <f>'Asignación'!E7</f>
+        <f>IF('Asignación'!E7="","",'Asignación'!E7)</f>
         <v/>
       </c>
       <c r="J4">
-        <f>'Asignación'!F7</f>
+        <f>IF('Asignación'!F7="","",'Asignación'!F7)</f>
         <v/>
       </c>
       <c r="L4">
-        <f>IF('Asignación'!$G$7="","",'Asignación'!$G$7&amp;"|"&amp;'Asignación'!$A$7)</f>
+        <f>IF(OR('Asignación'!$G$7="",'Asignación'!$A$7=""),"",'Asignación'!$G$7&amp;"|"&amp;'Asignación'!$A$7)</f>
         <v/>
       </c>
       <c r="M4">
@@ -5564,23 +5564,23 @@
         <v/>
       </c>
       <c r="G5">
-        <f>'Asignación'!B8</f>
+        <f>IF('Asignación'!B8="","",'Asignación'!B8)</f>
         <v/>
       </c>
       <c r="H5">
-        <f>'Asignación'!D8</f>
+        <f>IF('Asignación'!D8="","",'Asignación'!D8)</f>
         <v/>
       </c>
       <c r="I5">
-        <f>'Asignación'!E8</f>
+        <f>IF('Asignación'!E8="","",'Asignación'!E8)</f>
         <v/>
       </c>
       <c r="J5">
-        <f>'Asignación'!F8</f>
+        <f>IF('Asignación'!F8="","",'Asignación'!F8)</f>
         <v/>
       </c>
       <c r="L5">
-        <f>IF('Asignación'!$G$8="","",'Asignación'!$G$8&amp;"|"&amp;'Asignación'!$A$8)</f>
+        <f>IF(OR('Asignación'!$G$8="",'Asignación'!$A$8=""),"",'Asignación'!$G$8&amp;"|"&amp;'Asignación'!$A$8)</f>
         <v/>
       </c>
       <c r="M5">
@@ -5594,23 +5594,23 @@
         <v/>
       </c>
       <c r="G6">
-        <f>'Asignación'!B9</f>
+        <f>IF('Asignación'!B9="","",'Asignación'!B9)</f>
         <v/>
       </c>
       <c r="H6">
-        <f>'Asignación'!D9</f>
+        <f>IF('Asignación'!D9="","",'Asignación'!D9)</f>
         <v/>
       </c>
       <c r="I6">
-        <f>'Asignación'!E9</f>
+        <f>IF('Asignación'!E9="","",'Asignación'!E9)</f>
         <v/>
       </c>
       <c r="J6">
-        <f>'Asignación'!F9</f>
+        <f>IF('Asignación'!F9="","",'Asignación'!F9)</f>
         <v/>
       </c>
       <c r="L6">
-        <f>IF('Asignación'!$G$9="","",'Asignación'!$G$9&amp;"|"&amp;'Asignación'!$A$9)</f>
+        <f>IF(OR('Asignación'!$G$9="",'Asignación'!$A$9=""),"",'Asignación'!$G$9&amp;"|"&amp;'Asignación'!$A$9)</f>
         <v/>
       </c>
       <c r="M6">
@@ -5624,23 +5624,23 @@
         <v/>
       </c>
       <c r="G7">
-        <f>'Asignación'!B10</f>
+        <f>IF('Asignación'!B10="","",'Asignación'!B10)</f>
         <v/>
       </c>
       <c r="H7">
-        <f>'Asignación'!D10</f>
+        <f>IF('Asignación'!D10="","",'Asignación'!D10)</f>
         <v/>
       </c>
       <c r="I7">
-        <f>'Asignación'!E10</f>
+        <f>IF('Asignación'!E10="","",'Asignación'!E10)</f>
         <v/>
       </c>
       <c r="J7">
-        <f>'Asignación'!F10</f>
+        <f>IF('Asignación'!F10="","",'Asignación'!F10)</f>
         <v/>
       </c>
       <c r="L7">
-        <f>IF('Asignación'!$G$10="","",'Asignación'!$G$10&amp;"|"&amp;'Asignación'!$A$10)</f>
+        <f>IF(OR('Asignación'!$G$10="",'Asignación'!$A$10=""),"",'Asignación'!$G$10&amp;"|"&amp;'Asignación'!$A$10)</f>
         <v/>
       </c>
       <c r="M7">
@@ -5654,23 +5654,23 @@
         <v/>
       </c>
       <c r="G8">
-        <f>'Asignación'!B11</f>
+        <f>IF('Asignación'!B11="","",'Asignación'!B11)</f>
         <v/>
       </c>
       <c r="H8">
-        <f>'Asignación'!D11</f>
+        <f>IF('Asignación'!D11="","",'Asignación'!D11)</f>
         <v/>
       </c>
       <c r="I8">
-        <f>'Asignación'!E11</f>
+        <f>IF('Asignación'!E11="","",'Asignación'!E11)</f>
         <v/>
       </c>
       <c r="J8">
-        <f>'Asignación'!F11</f>
+        <f>IF('Asignación'!F11="","",'Asignación'!F11)</f>
         <v/>
       </c>
       <c r="L8">
-        <f>IF('Asignación'!$G$11="","",'Asignación'!$G$11&amp;"|"&amp;'Asignación'!$A$11)</f>
+        <f>IF(OR('Asignación'!$G$11="",'Asignación'!$A$11=""),"",'Asignación'!$G$11&amp;"|"&amp;'Asignación'!$A$11)</f>
         <v/>
       </c>
       <c r="M8">
@@ -5684,23 +5684,23 @@
         <v/>
       </c>
       <c r="G9">
-        <f>'Asignación'!B12</f>
+        <f>IF('Asignación'!B12="","",'Asignación'!B12)</f>
         <v/>
       </c>
       <c r="H9">
-        <f>'Asignación'!D12</f>
+        <f>IF('Asignación'!D12="","",'Asignación'!D12)</f>
         <v/>
       </c>
       <c r="I9">
-        <f>'Asignación'!E12</f>
+        <f>IF('Asignación'!E12="","",'Asignación'!E12)</f>
         <v/>
       </c>
       <c r="J9">
-        <f>'Asignación'!F12</f>
+        <f>IF('Asignación'!F12="","",'Asignación'!F12)</f>
         <v/>
       </c>
       <c r="L9">
-        <f>IF('Asignación'!$G$12="","",'Asignación'!$G$12&amp;"|"&amp;'Asignación'!$A$12)</f>
+        <f>IF(OR('Asignación'!$G$12="",'Asignación'!$A$12=""),"",'Asignación'!$G$12&amp;"|"&amp;'Asignación'!$A$12)</f>
         <v/>
       </c>
       <c r="M9">
@@ -5714,23 +5714,23 @@
         <v/>
       </c>
       <c r="G10">
-        <f>'Asignación'!B13</f>
+        <f>IF('Asignación'!B13="","",'Asignación'!B13)</f>
         <v/>
       </c>
       <c r="H10">
-        <f>'Asignación'!D13</f>
+        <f>IF('Asignación'!D13="","",'Asignación'!D13)</f>
         <v/>
       </c>
       <c r="I10">
-        <f>'Asignación'!E13</f>
+        <f>IF('Asignación'!E13="","",'Asignación'!E13)</f>
         <v/>
       </c>
       <c r="J10">
-        <f>'Asignación'!F13</f>
+        <f>IF('Asignación'!F13="","",'Asignación'!F13)</f>
         <v/>
       </c>
       <c r="L10">
-        <f>IF('Asignación'!$G$13="","",'Asignación'!$G$13&amp;"|"&amp;'Asignación'!$A$13)</f>
+        <f>IF(OR('Asignación'!$G$13="",'Asignación'!$A$13=""),"",'Asignación'!$G$13&amp;"|"&amp;'Asignación'!$A$13)</f>
         <v/>
       </c>
       <c r="M10">
@@ -5744,23 +5744,23 @@
         <v/>
       </c>
       <c r="G11">
-        <f>'Asignación'!B14</f>
+        <f>IF('Asignación'!B14="","",'Asignación'!B14)</f>
         <v/>
       </c>
       <c r="H11">
-        <f>'Asignación'!D14</f>
+        <f>IF('Asignación'!D14="","",'Asignación'!D14)</f>
         <v/>
       </c>
       <c r="I11">
-        <f>'Asignación'!E14</f>
+        <f>IF('Asignación'!E14="","",'Asignación'!E14)</f>
         <v/>
       </c>
       <c r="J11">
-        <f>'Asignación'!F14</f>
+        <f>IF('Asignación'!F14="","",'Asignación'!F14)</f>
         <v/>
       </c>
       <c r="L11">
-        <f>IF('Asignación'!$G$14="","",'Asignación'!$G$14&amp;"|"&amp;'Asignación'!$A$14)</f>
+        <f>IF(OR('Asignación'!$G$14="",'Asignación'!$A$14=""),"",'Asignación'!$G$14&amp;"|"&amp;'Asignación'!$A$14)</f>
         <v/>
       </c>
       <c r="M11">
@@ -5774,23 +5774,23 @@
         <v/>
       </c>
       <c r="G12">
-        <f>'Asignación'!B15</f>
+        <f>IF('Asignación'!B15="","",'Asignación'!B15)</f>
         <v/>
       </c>
       <c r="H12">
-        <f>'Asignación'!D15</f>
+        <f>IF('Asignación'!D15="","",'Asignación'!D15)</f>
         <v/>
       </c>
       <c r="I12">
-        <f>'Asignación'!E15</f>
+        <f>IF('Asignación'!E15="","",'Asignación'!E15)</f>
         <v/>
       </c>
       <c r="J12">
-        <f>'Asignación'!F15</f>
+        <f>IF('Asignación'!F15="","",'Asignación'!F15)</f>
         <v/>
       </c>
       <c r="L12">
-        <f>IF('Asignación'!$G$15="","",'Asignación'!$G$15&amp;"|"&amp;'Asignación'!$A$15)</f>
+        <f>IF(OR('Asignación'!$G$15="",'Asignación'!$A$15=""),"",'Asignación'!$G$15&amp;"|"&amp;'Asignación'!$A$15)</f>
         <v/>
       </c>
       <c r="M12">
@@ -5804,23 +5804,23 @@
         <v/>
       </c>
       <c r="G13">
-        <f>'Asignación'!B16</f>
+        <f>IF('Asignación'!B16="","",'Asignación'!B16)</f>
         <v/>
       </c>
       <c r="H13">
-        <f>'Asignación'!D16</f>
+        <f>IF('Asignación'!D16="","",'Asignación'!D16)</f>
         <v/>
       </c>
       <c r="I13">
-        <f>'Asignación'!E16</f>
+        <f>IF('Asignación'!E16="","",'Asignación'!E16)</f>
         <v/>
       </c>
       <c r="J13">
-        <f>'Asignación'!F16</f>
+        <f>IF('Asignación'!F16="","",'Asignación'!F16)</f>
         <v/>
       </c>
       <c r="L13">
-        <f>IF('Asignación'!$G$16="","",'Asignación'!$G$16&amp;"|"&amp;'Asignación'!$A$16)</f>
+        <f>IF(OR('Asignación'!$G$16="",'Asignación'!$A$16=""),"",'Asignación'!$G$16&amp;"|"&amp;'Asignación'!$A$16)</f>
         <v/>
       </c>
       <c r="M13">
@@ -5834,23 +5834,23 @@
         <v/>
       </c>
       <c r="G14">
-        <f>'Asignación'!B17</f>
+        <f>IF('Asignación'!B17="","",'Asignación'!B17)</f>
         <v/>
       </c>
       <c r="H14">
-        <f>'Asignación'!D17</f>
+        <f>IF('Asignación'!D17="","",'Asignación'!D17)</f>
         <v/>
       </c>
       <c r="I14">
-        <f>'Asignación'!E17</f>
+        <f>IF('Asignación'!E17="","",'Asignación'!E17)</f>
         <v/>
       </c>
       <c r="J14">
-        <f>'Asignación'!F17</f>
+        <f>IF('Asignación'!F17="","",'Asignación'!F17)</f>
         <v/>
       </c>
       <c r="L14">
-        <f>IF('Asignación'!$G$17="","",'Asignación'!$G$17&amp;"|"&amp;'Asignación'!$A$17)</f>
+        <f>IF(OR('Asignación'!$G$17="",'Asignación'!$A$17=""),"",'Asignación'!$G$17&amp;"|"&amp;'Asignación'!$A$17)</f>
         <v/>
       </c>
       <c r="M14">
@@ -5864,23 +5864,23 @@
         <v/>
       </c>
       <c r="G15">
-        <f>'Asignación'!B18</f>
+        <f>IF('Asignación'!B18="","",'Asignación'!B18)</f>
         <v/>
       </c>
       <c r="H15">
-        <f>'Asignación'!D18</f>
+        <f>IF('Asignación'!D18="","",'Asignación'!D18)</f>
         <v/>
       </c>
       <c r="I15">
-        <f>'Asignación'!E18</f>
+        <f>IF('Asignación'!E18="","",'Asignación'!E18)</f>
         <v/>
       </c>
       <c r="J15">
-        <f>'Asignación'!F18</f>
+        <f>IF('Asignación'!F18="","",'Asignación'!F18)</f>
         <v/>
       </c>
       <c r="L15">
-        <f>IF('Asignación'!$G$18="","",'Asignación'!$G$18&amp;"|"&amp;'Asignación'!$A$18)</f>
+        <f>IF(OR('Asignación'!$G$18="",'Asignación'!$A$18=""),"",'Asignación'!$G$18&amp;"|"&amp;'Asignación'!$A$18)</f>
         <v/>
       </c>
       <c r="M15">
@@ -5894,23 +5894,23 @@
         <v/>
       </c>
       <c r="G16">
-        <f>'Asignación'!B19</f>
+        <f>IF('Asignación'!B19="","",'Asignación'!B19)</f>
         <v/>
       </c>
       <c r="H16">
-        <f>'Asignación'!D19</f>
+        <f>IF('Asignación'!D19="","",'Asignación'!D19)</f>
         <v/>
       </c>
       <c r="I16">
-        <f>'Asignación'!E19</f>
+        <f>IF('Asignación'!E19="","",'Asignación'!E19)</f>
         <v/>
       </c>
       <c r="J16">
-        <f>'Asignación'!F19</f>
+        <f>IF('Asignación'!F19="","",'Asignación'!F19)</f>
         <v/>
       </c>
       <c r="L16">
-        <f>IF('Asignación'!$G$19="","",'Asignación'!$G$19&amp;"|"&amp;'Asignación'!$A$19)</f>
+        <f>IF(OR('Asignación'!$G$19="",'Asignación'!$A$19=""),"",'Asignación'!$G$19&amp;"|"&amp;'Asignación'!$A$19)</f>
         <v/>
       </c>
       <c r="M16">
@@ -5924,23 +5924,23 @@
         <v/>
       </c>
       <c r="G17">
-        <f>'Asignación'!B20</f>
+        <f>IF('Asignación'!B20="","",'Asignación'!B20)</f>
         <v/>
       </c>
       <c r="H17">
-        <f>'Asignación'!D20</f>
+        <f>IF('Asignación'!D20="","",'Asignación'!D20)</f>
         <v/>
       </c>
       <c r="I17">
-        <f>'Asignación'!E20</f>
+        <f>IF('Asignación'!E20="","",'Asignación'!E20)</f>
         <v/>
       </c>
       <c r="J17">
-        <f>'Asignación'!F20</f>
+        <f>IF('Asignación'!F20="","",'Asignación'!F20)</f>
         <v/>
       </c>
       <c r="L17">
-        <f>IF('Asignación'!$G$20="","",'Asignación'!$G$20&amp;"|"&amp;'Asignación'!$A$20)</f>
+        <f>IF(OR('Asignación'!$G$20="",'Asignación'!$A$20=""),"",'Asignación'!$G$20&amp;"|"&amp;'Asignación'!$A$20)</f>
         <v/>
       </c>
       <c r="M17">
@@ -5954,23 +5954,23 @@
         <v/>
       </c>
       <c r="G18">
-        <f>'Asignación'!B21</f>
+        <f>IF('Asignación'!B21="","",'Asignación'!B21)</f>
         <v/>
       </c>
       <c r="H18">
-        <f>'Asignación'!D21</f>
+        <f>IF('Asignación'!D21="","",'Asignación'!D21)</f>
         <v/>
       </c>
       <c r="I18">
-        <f>'Asignación'!E21</f>
+        <f>IF('Asignación'!E21="","",'Asignación'!E21)</f>
         <v/>
       </c>
       <c r="J18">
-        <f>'Asignación'!F21</f>
+        <f>IF('Asignación'!F21="","",'Asignación'!F21)</f>
         <v/>
       </c>
       <c r="L18">
-        <f>IF('Asignación'!$G$21="","",'Asignación'!$G$21&amp;"|"&amp;'Asignación'!$A$21)</f>
+        <f>IF(OR('Asignación'!$G$21="",'Asignación'!$A$21=""),"",'Asignación'!$G$21&amp;"|"&amp;'Asignación'!$A$21)</f>
         <v/>
       </c>
       <c r="M18">
@@ -5984,23 +5984,23 @@
         <v/>
       </c>
       <c r="G19">
-        <f>'Asignación'!B22</f>
+        <f>IF('Asignación'!B22="","",'Asignación'!B22)</f>
         <v/>
       </c>
       <c r="H19">
-        <f>'Asignación'!D22</f>
+        <f>IF('Asignación'!D22="","",'Asignación'!D22)</f>
         <v/>
       </c>
       <c r="I19">
-        <f>'Asignación'!E22</f>
+        <f>IF('Asignación'!E22="","",'Asignación'!E22)</f>
         <v/>
       </c>
       <c r="J19">
-        <f>'Asignación'!F22</f>
+        <f>IF('Asignación'!F22="","",'Asignación'!F22)</f>
         <v/>
       </c>
       <c r="L19">
-        <f>IF('Asignación'!$G$22="","",'Asignación'!$G$22&amp;"|"&amp;'Asignación'!$A$22)</f>
+        <f>IF(OR('Asignación'!$G$22="",'Asignación'!$A$22=""),"",'Asignación'!$G$22&amp;"|"&amp;'Asignación'!$A$22)</f>
         <v/>
       </c>
       <c r="M19">
@@ -6014,23 +6014,23 @@
         <v/>
       </c>
       <c r="G20">
-        <f>'Asignación'!B23</f>
+        <f>IF('Asignación'!B23="","",'Asignación'!B23)</f>
         <v/>
       </c>
       <c r="H20">
-        <f>'Asignación'!D23</f>
+        <f>IF('Asignación'!D23="","",'Asignación'!D23)</f>
         <v/>
       </c>
       <c r="I20">
-        <f>'Asignación'!E23</f>
+        <f>IF('Asignación'!E23="","",'Asignación'!E23)</f>
         <v/>
       </c>
       <c r="J20">
-        <f>'Asignación'!F23</f>
+        <f>IF('Asignación'!F23="","",'Asignación'!F23)</f>
         <v/>
       </c>
       <c r="L20">
-        <f>IF('Asignación'!$G$23="","",'Asignación'!$G$23&amp;"|"&amp;'Asignación'!$A$23)</f>
+        <f>IF(OR('Asignación'!$G$23="",'Asignación'!$A$23=""),"",'Asignación'!$G$23&amp;"|"&amp;'Asignación'!$A$23)</f>
         <v/>
       </c>
       <c r="M20">
@@ -6044,23 +6044,23 @@
         <v/>
       </c>
       <c r="G21">
-        <f>'Asignación'!B24</f>
+        <f>IF('Asignación'!B24="","",'Asignación'!B24)</f>
         <v/>
       </c>
       <c r="H21">
-        <f>'Asignación'!D24</f>
+        <f>IF('Asignación'!D24="","",'Asignación'!D24)</f>
         <v/>
       </c>
       <c r="I21">
-        <f>'Asignación'!E24</f>
+        <f>IF('Asignación'!E24="","",'Asignación'!E24)</f>
         <v/>
       </c>
       <c r="J21">
-        <f>'Asignación'!F24</f>
+        <f>IF('Asignación'!F24="","",'Asignación'!F24)</f>
         <v/>
       </c>
       <c r="L21">
-        <f>IF('Asignación'!$G$24="","",'Asignación'!$G$24&amp;"|"&amp;'Asignación'!$A$24)</f>
+        <f>IF(OR('Asignación'!$G$24="",'Asignación'!$A$24=""),"",'Asignación'!$G$24&amp;"|"&amp;'Asignación'!$A$24)</f>
         <v/>
       </c>
       <c r="M21">
@@ -6074,23 +6074,23 @@
         <v/>
       </c>
       <c r="G22">
-        <f>'Asignación'!B25</f>
+        <f>IF('Asignación'!B25="","",'Asignación'!B25)</f>
         <v/>
       </c>
       <c r="H22">
-        <f>'Asignación'!D25</f>
+        <f>IF('Asignación'!D25="","",'Asignación'!D25)</f>
         <v/>
       </c>
       <c r="I22">
-        <f>'Asignación'!E25</f>
+        <f>IF('Asignación'!E25="","",'Asignación'!E25)</f>
         <v/>
       </c>
       <c r="J22">
-        <f>'Asignación'!F25</f>
+        <f>IF('Asignación'!F25="","",'Asignación'!F25)</f>
         <v/>
       </c>
       <c r="L22">
-        <f>IF('Asignación'!$G$25="","",'Asignación'!$G$25&amp;"|"&amp;'Asignación'!$A$25)</f>
+        <f>IF(OR('Asignación'!$G$25="",'Asignación'!$A$25=""),"",'Asignación'!$G$25&amp;"|"&amp;'Asignación'!$A$25)</f>
         <v/>
       </c>
       <c r="M22">
@@ -6104,23 +6104,23 @@
         <v/>
       </c>
       <c r="G23">
-        <f>'Asignación'!B26</f>
+        <f>IF('Asignación'!B26="","",'Asignación'!B26)</f>
         <v/>
       </c>
       <c r="H23">
-        <f>'Asignación'!D26</f>
+        <f>IF('Asignación'!D26="","",'Asignación'!D26)</f>
         <v/>
       </c>
       <c r="I23">
-        <f>'Asignación'!E26</f>
+        <f>IF('Asignación'!E26="","",'Asignación'!E26)</f>
         <v/>
       </c>
       <c r="J23">
-        <f>'Asignación'!F26</f>
+        <f>IF('Asignación'!F26="","",'Asignación'!F26)</f>
         <v/>
       </c>
       <c r="L23">
-        <f>IF('Asignación'!$G$26="","",'Asignación'!$G$26&amp;"|"&amp;'Asignación'!$A$26)</f>
+        <f>IF(OR('Asignación'!$G$26="",'Asignación'!$A$26=""),"",'Asignación'!$G$26&amp;"|"&amp;'Asignación'!$A$26)</f>
         <v/>
       </c>
       <c r="M23">
@@ -6134,23 +6134,23 @@
         <v/>
       </c>
       <c r="G24">
-        <f>'Asignación'!B27</f>
+        <f>IF('Asignación'!B27="","",'Asignación'!B27)</f>
         <v/>
       </c>
       <c r="H24">
-        <f>'Asignación'!D27</f>
+        <f>IF('Asignación'!D27="","",'Asignación'!D27)</f>
         <v/>
       </c>
       <c r="I24">
-        <f>'Asignación'!E27</f>
+        <f>IF('Asignación'!E27="","",'Asignación'!E27)</f>
         <v/>
       </c>
       <c r="J24">
-        <f>'Asignación'!F27</f>
+        <f>IF('Asignación'!F27="","",'Asignación'!F27)</f>
         <v/>
       </c>
       <c r="L24">
-        <f>IF('Asignación'!$G$27="","",'Asignación'!$G$27&amp;"|"&amp;'Asignación'!$A$27)</f>
+        <f>IF(OR('Asignación'!$G$27="",'Asignación'!$A$27=""),"",'Asignación'!$G$27&amp;"|"&amp;'Asignación'!$A$27)</f>
         <v/>
       </c>
       <c r="M24">
@@ -6164,23 +6164,23 @@
         <v/>
       </c>
       <c r="G25">
-        <f>'Asignación'!B28</f>
+        <f>IF('Asignación'!B28="","",'Asignación'!B28)</f>
         <v/>
       </c>
       <c r="H25">
-        <f>'Asignación'!D28</f>
+        <f>IF('Asignación'!D28="","",'Asignación'!D28)</f>
         <v/>
       </c>
       <c r="I25">
-        <f>'Asignación'!E28</f>
+        <f>IF('Asignación'!E28="","",'Asignación'!E28)</f>
         <v/>
       </c>
       <c r="J25">
-        <f>'Asignación'!F28</f>
+        <f>IF('Asignación'!F28="","",'Asignación'!F28)</f>
         <v/>
       </c>
       <c r="L25">
-        <f>IF('Asignación'!$G$28="","",'Asignación'!$G$28&amp;"|"&amp;'Asignación'!$A$28)</f>
+        <f>IF(OR('Asignación'!$G$28="",'Asignación'!$A$28=""),"",'Asignación'!$G$28&amp;"|"&amp;'Asignación'!$A$28)</f>
         <v/>
       </c>
       <c r="M25">
@@ -6194,23 +6194,23 @@
         <v/>
       </c>
       <c r="G26">
-        <f>'Asignación'!B29</f>
+        <f>IF('Asignación'!B29="","",'Asignación'!B29)</f>
         <v/>
       </c>
       <c r="H26">
-        <f>'Asignación'!D29</f>
+        <f>IF('Asignación'!D29="","",'Asignación'!D29)</f>
         <v/>
       </c>
       <c r="I26">
-        <f>'Asignación'!E29</f>
+        <f>IF('Asignación'!E29="","",'Asignación'!E29)</f>
         <v/>
       </c>
       <c r="J26">
-        <f>'Asignación'!F29</f>
+        <f>IF('Asignación'!F29="","",'Asignación'!F29)</f>
         <v/>
       </c>
       <c r="L26">
-        <f>IF('Asignación'!$G$29="","",'Asignación'!$G$29&amp;"|"&amp;'Asignación'!$A$29)</f>
+        <f>IF(OR('Asignación'!$G$29="",'Asignación'!$A$29=""),"",'Asignación'!$G$29&amp;"|"&amp;'Asignación'!$A$29)</f>
         <v/>
       </c>
       <c r="M26">
@@ -6224,23 +6224,23 @@
         <v/>
       </c>
       <c r="G27">
-        <f>'Asignación'!B30</f>
+        <f>IF('Asignación'!B30="","",'Asignación'!B30)</f>
         <v/>
       </c>
       <c r="H27">
-        <f>'Asignación'!D30</f>
+        <f>IF('Asignación'!D30="","",'Asignación'!D30)</f>
         <v/>
       </c>
       <c r="I27">
-        <f>'Asignación'!E30</f>
+        <f>IF('Asignación'!E30="","",'Asignación'!E30)</f>
         <v/>
       </c>
       <c r="J27">
-        <f>'Asignación'!F30</f>
+        <f>IF('Asignación'!F30="","",'Asignación'!F30)</f>
         <v/>
       </c>
       <c r="L27">
-        <f>IF('Asignación'!$G$30="","",'Asignación'!$G$30&amp;"|"&amp;'Asignación'!$A$30)</f>
+        <f>IF(OR('Asignación'!$G$30="",'Asignación'!$A$30=""),"",'Asignación'!$G$30&amp;"|"&amp;'Asignación'!$A$30)</f>
         <v/>
       </c>
       <c r="M27">
@@ -6254,23 +6254,23 @@
         <v/>
       </c>
       <c r="G28">
-        <f>'Asignación'!B31</f>
+        <f>IF('Asignación'!B31="","",'Asignación'!B31)</f>
         <v/>
       </c>
       <c r="H28">
-        <f>'Asignación'!D31</f>
+        <f>IF('Asignación'!D31="","",'Asignación'!D31)</f>
         <v/>
       </c>
       <c r="I28">
-        <f>'Asignación'!E31</f>
+        <f>IF('Asignación'!E31="","",'Asignación'!E31)</f>
         <v/>
       </c>
       <c r="J28">
-        <f>'Asignación'!F31</f>
+        <f>IF('Asignación'!F31="","",'Asignación'!F31)</f>
         <v/>
       </c>
       <c r="L28">
-        <f>IF('Asignación'!$G$31="","",'Asignación'!$G$31&amp;"|"&amp;'Asignación'!$A$31)</f>
+        <f>IF(OR('Asignación'!$G$31="",'Asignación'!$A$31=""),"",'Asignación'!$G$31&amp;"|"&amp;'Asignación'!$A$31)</f>
         <v/>
       </c>
       <c r="M28">
@@ -6284,23 +6284,23 @@
         <v/>
       </c>
       <c r="G29">
-        <f>'Asignación'!B32</f>
+        <f>IF('Asignación'!B32="","",'Asignación'!B32)</f>
         <v/>
       </c>
       <c r="H29">
-        <f>'Asignación'!D32</f>
+        <f>IF('Asignación'!D32="","",'Asignación'!D32)</f>
         <v/>
       </c>
       <c r="I29">
-        <f>'Asignación'!E32</f>
+        <f>IF('Asignación'!E32="","",'Asignación'!E32)</f>
         <v/>
       </c>
       <c r="J29">
-        <f>'Asignación'!F32</f>
+        <f>IF('Asignación'!F32="","",'Asignación'!F32)</f>
         <v/>
       </c>
       <c r="L29">
-        <f>IF('Asignación'!$G$32="","",'Asignación'!$G$32&amp;"|"&amp;'Asignación'!$A$32)</f>
+        <f>IF(OR('Asignación'!$G$32="",'Asignación'!$A$32=""),"",'Asignación'!$G$32&amp;"|"&amp;'Asignación'!$A$32)</f>
         <v/>
       </c>
       <c r="M29">
@@ -6314,23 +6314,23 @@
         <v/>
       </c>
       <c r="G30">
-        <f>'Asignación'!B33</f>
+        <f>IF('Asignación'!B33="","",'Asignación'!B33)</f>
         <v/>
       </c>
       <c r="H30">
-        <f>'Asignación'!D33</f>
+        <f>IF('Asignación'!D33="","",'Asignación'!D33)</f>
         <v/>
       </c>
       <c r="I30">
-        <f>'Asignación'!E33</f>
+        <f>IF('Asignación'!E33="","",'Asignación'!E33)</f>
         <v/>
       </c>
       <c r="J30">
-        <f>'Asignación'!F33</f>
+        <f>IF('Asignación'!F33="","",'Asignación'!F33)</f>
         <v/>
       </c>
       <c r="L30">
-        <f>IF('Asignación'!$G$33="","",'Asignación'!$G$33&amp;"|"&amp;'Asignación'!$A$33)</f>
+        <f>IF(OR('Asignación'!$G$33="",'Asignación'!$A$33=""),"",'Asignación'!$G$33&amp;"|"&amp;'Asignación'!$A$33)</f>
         <v/>
       </c>
       <c r="M30">
